--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120833960</v>
+        <v>120833466</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539868</v>
+        <v>539952</v>
       </c>
       <c r="R2" t="n">
-        <v>6736744</v>
+        <v>6736772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120833466</v>
+        <v>120833460</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,40 +813,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539952</v>
+        <v>539950</v>
       </c>
       <c r="R3" t="n">
-        <v>6736772</v>
+        <v>6736771</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120833460</v>
+        <v>120833960</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,30 +929,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539950</v>
+        <v>539868</v>
       </c>
       <c r="R4" t="n">
-        <v>6736771</v>
+        <v>6736744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1041,228 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122528492</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78652</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539868</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6736775</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122528405</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56589</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>539868</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6736775</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>122528492</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,6 +1060,11 @@
       </c>
       <c r="E5" t="n">
         <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1153,7 +1158,7 @@
         <v>122528405</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,6 +1172,11 @@
       </c>
       <c r="E6" t="n">
         <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528492</v>
+        <v>122528405</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,28 +1055,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1118,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,17 +1156,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528405</v>
+        <v>122528335</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,36 +1175,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1268,242 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122529444</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>539904</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6736748</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122528449</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539904</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6736748</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528335</v>
+        <v>122528411</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528405</v>
+        <v>122528335</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,36 +1055,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,17 +1148,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528411</v>
+        <v>122528405</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,28 +1167,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528335</v>
+        <v>122528492</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122529444</v>
+        <v>122528449</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,24 +1291,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528449</v>
+        <v>122529444</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,32 +1411,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528492</v>
+        <v>122528405</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,28 +1055,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1118,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,17 +1156,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528405</v>
+        <v>122528411</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,36 +1175,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122528449</v>
+        <v>122529444</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,32 +1291,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1358,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122529444</v>
+        <v>122528449</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,24 +1403,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1166,7 +1166,7 @@
         <v>122528411</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>122529444</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528405</v>
+        <v>122528335</v>
       </c>
       <c r="B5" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,36 +1055,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,17 +1148,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528411</v>
+        <v>122528405</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,28 +1167,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>122529444</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1166,7 +1166,7 @@
         <v>122528492</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528405</v>
+        <v>122528411</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,36 +1055,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,17 +1148,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528492</v>
+        <v>122528405</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,28 +1167,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528411</v>
+        <v>122528492</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122529444</v>
+        <v>122528449</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,24 +1291,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528449</v>
+        <v>122529444</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,32 +1411,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122528492</v>
+        <v>122528335</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122528449</v>
+        <v>122529444</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,32 +1291,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1358,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122529444</v>
+        <v>122528449</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,24 +1403,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120833466</v>
+        <v>120836634</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539952</v>
+        <v>539959</v>
       </c>
       <c r="R2" t="n">
-        <v>6736772</v>
+        <v>6736793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,16 +794,11 @@
         <v>120833460</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -917,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120833960</v>
+        <v>120834047</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,48 +913,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539868</v>
+        <v>539869</v>
       </c>
       <c r="R4" t="n">
-        <v>6736744</v>
+        <v>6736736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1046,16 +1020,11 @@
         <v>122528335</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1155,58 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528405</v>
+        <v>122529444</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539868</v>
+        <v>539904</v>
       </c>
       <c r="R6" t="n">
-        <v>6736775</v>
+        <v>6736748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1204,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,52 +1219,55 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122529444</v>
+        <v>122528449</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsvånkan, Långsvånkan, Dlr</t>
@@ -1350,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,37 +1346,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528449</v>
+        <v>122528405</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,7 +1379,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1435,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539904</v>
+        <v>539868</v>
       </c>
       <c r="R8" t="n">
-        <v>6736748</v>
+        <v>6736775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,15 +1449,372 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122529232</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>539972</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6736750</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120833466</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>539952</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6736772</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120833960</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långsvånkan, Långsvånkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>539868</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6736744</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14878-2024 artfynd.xlsx
+++ b/artfynd/A 14878-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120836634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120833460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120834047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122528335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122529444</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122528449</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122528405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122529232</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120833466</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,8 +1865,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120833960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>